--- a/data/Plan N 10x-1.xlsx
+++ b/data/Plan N 10x-1.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.2495</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>83.7831</t>
+          <t>0.0250</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,7 +510,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Lum</t>
         </is>
       </c>
     </row>
@@ -524,3370 +524,3834 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7.934946089485372</v>
+        <v>0.002092217989607952</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9745763893142533</v>
+        <v>0.975563035276458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15.86989217897074</v>
+        <v>0.004184435979215904</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9244452637412834</v>
+        <v>0.9327671875632755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23.80483826845612</v>
+        <v>0.006276653968823856</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8753243852739103</v>
+        <v>0.892777464149017</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>31.73978435794149</v>
+        <v>0.008368871958431808</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8151838400790447</v>
+        <v>0.8420360674033037</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>39.67473044742686</v>
+        <v>0.01046108994803976</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7534857277346881</v>
+        <v>0.7880930696270912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47.60967653691223</v>
+        <v>0.01255330793764771</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6970379929554722</v>
+        <v>0.7353687154708528</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55.5446226263976</v>
+        <v>0.01464552592725566</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6413443707683628</v>
+        <v>0.6855254368534731</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63.47956871588298</v>
+        <v>0.01673774391686362</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5931701111683712</v>
+        <v>0.6384921897102434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71.41451480536834</v>
+        <v>0.01882996190647157</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5521233559166528</v>
+        <v>0.59485513169733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79.34946089485372</v>
+        <v>0.02092217989607952</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5172473629583881</v>
+        <v>0.5589197920152074</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87.28440698433909</v>
+        <v>0.02301439788568747</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4863796765713612</v>
+        <v>0.5267675283858466</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95.21935307382446</v>
+        <v>0.02510661587529543</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4583777883557852</v>
+        <v>0.4991176066035576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103.1542991633098</v>
+        <v>0.02719883386490338</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4354208646946742</v>
+        <v>0.4720836037632022</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111.0892452527952</v>
+        <v>0.02929105185451133</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4123611637706981</v>
+        <v>0.4480265802694992</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119.0241913422806</v>
+        <v>0.03138326984411928</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3879011894018638</v>
+        <v>0.4292295539172274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126.959137431766</v>
+        <v>0.03347548783372723</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3705545844922815</v>
+        <v>0.4090114185767951</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134.8940835212513</v>
+        <v>0.03556770582333518</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3536083864202934</v>
+        <v>0.3884784568920187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>142.8290296107367</v>
+        <v>0.03765992381294313</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3355097189582452</v>
+        <v>0.3728934770954808</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>150.7639757002221</v>
+        <v>0.03975214180255109</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3195290623154239</v>
+        <v>0.3583838730872556</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>158.6989217897074</v>
+        <v>0.04184435979215904</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3021148647551549</v>
+        <v>0.3418356628791112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>166.6338678791928</v>
+        <v>0.04393657778176699</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2890731196737219</v>
+        <v>0.3273052019627076</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>174.5688139686782</v>
+        <v>0.04602879577137495</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2755472487394369</v>
+        <v>0.3130960619760858</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>182.5037600581636</v>
+        <v>0.0481210137609829</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2566921345274785</v>
+        <v>0.2974927031893684</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>190.4387061476489</v>
+        <v>0.05021323175059085</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2458395142948002</v>
+        <v>0.2860409456140669</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>198.3736522371343</v>
+        <v>0.0523054497401988</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2363453675576368</v>
+        <v>0.2760398228523828</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>206.3085983266197</v>
+        <v>0.05439766772980675</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2225821561379023</v>
+        <v>0.258751296591879</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>214.243544416105</v>
+        <v>0.0564898857194147</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2123966134353486</v>
+        <v>0.2462832794818155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>222.1784905055904</v>
+        <v>0.05858210370902266</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2000009652699251</v>
+        <v>0.2404684412359339</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>230.1134365950758</v>
+        <v>0.06067432169863061</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1879623264099039</v>
+        <v>0.2281914666344707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>238.0483826845611</v>
+        <v>0.06276653968823856</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1794847949800393</v>
+        <v>0.2175553466940332</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>245.9833287740465</v>
+        <v>0.06485875767784652</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1732076797732041</v>
+        <v>0.2094300728620244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>253.9182748635319</v>
+        <v>0.06695097566745446</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1662199348117186</v>
+        <v>0.1969628579781837</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>261.8532209530173</v>
+        <v>0.06904319365706242</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1558246950299254</v>
+        <v>0.1868352301970503</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>269.7881670425027</v>
+        <v>0.07113541164667037</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1504387733044987</v>
+        <v>0.1789066931543248</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>277.723113131988</v>
+        <v>0.07322762963627832</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1469449336826666</v>
+        <v>0.1729759533719532</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>285.6580592214734</v>
+        <v>0.07531984762588627</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1410504421581258</v>
+        <v>0.1694513415659617</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>293.5930053109587</v>
+        <v>0.07741206561549423</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1372350275923072</v>
+        <v>0.1601348494548129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>301.5279514004441</v>
+        <v>0.07950428360510217</v>
       </c>
       <c r="B40" t="n">
-        <v>0.132468344308833</v>
+        <v>0.1516085782178564</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>309.4628974899295</v>
+        <v>0.08159650159471013</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1271384963163708</v>
+        <v>0.1502246111822344</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>317.3978435794149</v>
+        <v>0.08368871958431807</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1225449993585415</v>
+        <v>0.1470307610924661</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>325.3327896689003</v>
+        <v>0.08578093757392603</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1190117315536998</v>
+        <v>0.1403056089686948</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>333.2677357583856</v>
+        <v>0.08787315556353398</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1170588826295392</v>
+        <v>0.1358259648546541</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>341.202681847871</v>
+        <v>0.08996537355314194</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1112030470260489</v>
+        <v>0.1327829108134928</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>349.1376279373563</v>
+        <v>0.09205759154274989</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1052112270805793</v>
+        <v>0.1297605233976529</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>357.0725740268417</v>
+        <v>0.09414980953235784</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1070256971995692</v>
+        <v>0.1251281605571365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>365.0075201163271</v>
+        <v>0.0962420275219658</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1133658298568929</v>
+        <v>0.1200604568583213</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>372.9424662058125</v>
+        <v>0.09833424551157374</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1119330444725208</v>
+        <v>0.1187277451769081</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>380.8774122952979</v>
+        <v>0.1004264635011817</v>
       </c>
       <c r="B50" t="n">
-        <v>0.10819542285484</v>
+        <v>0.1153003374766722</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>388.8123583847832</v>
+        <v>0.1025186814907896</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1064678605012423</v>
+        <v>0.108579368613272</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>396.7473044742686</v>
+        <v>0.1046108994803976</v>
       </c>
       <c r="B52" t="n">
-        <v>0.09716259346816294</v>
+        <v>0.1052166713236918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>404.6822505637539</v>
+        <v>0.1067031174700055</v>
       </c>
       <c r="B53" t="n">
-        <v>0.09605998695784226</v>
+        <v>0.105537701914029</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>412.6171966532393</v>
+        <v>0.1087953354596135</v>
       </c>
       <c r="B54" t="n">
-        <v>0.09929963544958754</v>
+        <v>0.1117021649076607</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>420.5521427427247</v>
+        <v>0.1108875534492215</v>
       </c>
       <c r="B55" t="n">
-        <v>0.09438695631172717</v>
+        <v>0.1153717171737031</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>428.4870888322101</v>
+        <v>0.1129797714388294</v>
       </c>
       <c r="B56" t="n">
-        <v>0.09039191085821006</v>
+        <v>0.1079909409443679</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>436.4220349216955</v>
+        <v>0.1150719894284374</v>
       </c>
       <c r="B57" t="n">
-        <v>0.08691253373672081</v>
+        <v>0.1072397561454657</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>444.3569810111808</v>
+        <v>0.1171642074180453</v>
       </c>
       <c r="B58" t="n">
-        <v>0.08464865354178337</v>
+        <v>0.1056760169138336</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>452.2919271006662</v>
+        <v>0.1192564254076533</v>
       </c>
       <c r="B59" t="n">
-        <v>0.08010581586177526</v>
+        <v>0.09365861465739389</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>460.2268731901515</v>
+        <v>0.1213486433972612</v>
       </c>
       <c r="B60" t="n">
-        <v>0.07483474148396967</v>
+        <v>0.09425459712301178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>468.1618192796369</v>
+        <v>0.1234408613868692</v>
       </c>
       <c r="B61" t="n">
-        <v>0.07704520494049612</v>
+        <v>0.09898468255172385</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>476.0967653691223</v>
+        <v>0.1255330793764771</v>
       </c>
       <c r="B62" t="n">
-        <v>0.07499095775917569</v>
+        <v>0.09461998175296309</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>484.0317114586077</v>
+        <v>0.1276252973660851</v>
       </c>
       <c r="B63" t="n">
-        <v>0.06978283980517339</v>
+        <v>0.09363574486790822</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>491.9666575480931</v>
+        <v>0.129717515355693</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0709475300742881</v>
+        <v>0.08644568646953459</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>499.9016036375784</v>
+        <v>0.131809733345301</v>
       </c>
       <c r="B65" t="n">
-        <v>0.07095236187179937</v>
+        <v>0.08040118560604759</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>507.8365497270638</v>
+        <v>0.1339019513349089</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0733063359070633</v>
+        <v>0.08705275145831308</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>515.7714958165492</v>
+        <v>0.1359941693245169</v>
       </c>
       <c r="B67" t="n">
-        <v>0.07707360236967482</v>
+        <v>0.07770611322804089</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>523.7064419060346</v>
+        <v>0.1380863873141248</v>
       </c>
       <c r="B68" t="n">
-        <v>0.07051132026340995</v>
+        <v>0.06832034183767779</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>531.6413879955199</v>
+        <v>0.1401786053037328</v>
       </c>
       <c r="B69" t="n">
-        <v>0.05965169174771007</v>
+        <v>0.07693268241494199</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>539.5763340850053</v>
+        <v>0.1422708232933407</v>
       </c>
       <c r="B70" t="n">
-        <v>0.05874569839813943</v>
+        <v>0.07523158625860127</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>547.5112801744906</v>
+        <v>0.1443630412829487</v>
       </c>
       <c r="B71" t="n">
-        <v>0.05963231384868845</v>
+        <v>0.06624403375902435</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>555.446226263976</v>
+        <v>0.1464552592725566</v>
       </c>
       <c r="B72" t="n">
-        <v>0.05603155121768583</v>
+        <v>0.06461330931185973</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>563.3811723534614</v>
+        <v>0.1485474772621646</v>
       </c>
       <c r="B73" t="n">
-        <v>0.05106969712215471</v>
+        <v>0.07196207895332506</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>571.3161184429467</v>
+        <v>0.1506396952517725</v>
       </c>
       <c r="B74" t="n">
-        <v>0.04521641593094188</v>
+        <v>0.07324511202552442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>579.2510645324321</v>
+        <v>0.1527319132413805</v>
       </c>
       <c r="B75" t="n">
-        <v>0.04813206597139038</v>
+        <v>0.07236552849952635</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>587.1860106219175</v>
+        <v>0.1548241312309885</v>
       </c>
       <c r="B76" t="n">
-        <v>0.04629549188476426</v>
+        <v>0.07663876587655892</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>595.1209567114029</v>
+        <v>0.1569163492205964</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03529725294546299</v>
+        <v>0.07314140448324298</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>603.0559028008882</v>
+        <v>0.1590085672102043</v>
       </c>
       <c r="B78" t="n">
-        <v>0.03382356296259383</v>
+        <v>0.058008578924014</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>610.9908488903736</v>
+        <v>0.1611007851998123</v>
       </c>
       <c r="B79" t="n">
-        <v>0.03324839709202004</v>
+        <v>0.05512148262140031</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>618.925794979859</v>
+        <v>0.1631930031894203</v>
       </c>
       <c r="B80" t="n">
-        <v>0.02987973476137438</v>
+        <v>0.05824805594537204</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>626.8607410693444</v>
+        <v>0.1652852211790282</v>
       </c>
       <c r="B81" t="n">
-        <v>0.02431574888810873</v>
+        <v>0.05340439048152094</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>634.7956871588298</v>
+        <v>0.1673774391686361</v>
       </c>
       <c r="B82" t="n">
-        <v>0.02702056009078045</v>
+        <v>0.05174077681209761</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>642.7306332483151</v>
+        <v>0.1694696571582441</v>
       </c>
       <c r="B83" t="n">
-        <v>0.03144082798089346</v>
+        <v>0.05380819048085849</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>650.6655793378005</v>
+        <v>0.1715618751478521</v>
       </c>
       <c r="B84" t="n">
-        <v>0.02820236235271128</v>
+        <v>0.04435069722501765</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>658.6005254272859</v>
+        <v>0.17365409313746</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0304895106103792</v>
+        <v>0.04551774049502936</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>666.5354715167712</v>
+        <v>0.175746311127068</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02398757107627101</v>
+        <v>0.04974208620717154</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>674.4704176062565</v>
+        <v>0.1778385291166759</v>
       </c>
       <c r="B87" t="n">
-        <v>0.01147307039549902</v>
+        <v>0.03614374130386041</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>682.4053636957419</v>
+        <v>0.1799307471062839</v>
       </c>
       <c r="B88" t="n">
-        <v>0.01455359944243025</v>
+        <v>0.0328333561646033</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>690.3403097852273</v>
+        <v>0.1820229650958918</v>
       </c>
       <c r="B89" t="n">
-        <v>0.01578021371159405</v>
+        <v>0.03736684494922496</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>698.2752558747127</v>
+        <v>0.1841151830854998</v>
       </c>
       <c r="B90" t="n">
-        <v>0.02379018090931448</v>
+        <v>0.03731398137982392</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>706.2102019641981</v>
+        <v>0.1862074010751077</v>
       </c>
       <c r="B91" t="n">
-        <v>0.02633641768664471</v>
+        <v>0.03435989458666654</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>714.1451480536834</v>
+        <v>0.1882996190647157</v>
       </c>
       <c r="B92" t="n">
-        <v>0.02237425496568907</v>
+        <v>0.01963564066420577</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>722.0800941431688</v>
+        <v>0.1903918370543236</v>
       </c>
       <c r="B93" t="n">
-        <v>0.01501559316323229</v>
+        <v>0.02310259605597731</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>730.0150402326542</v>
+        <v>0.1924840550439316</v>
       </c>
       <c r="B94" t="n">
-        <v>0.008233832615743697</v>
+        <v>0.03506157148162105</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>737.9499863221396</v>
+        <v>0.1945762730335395</v>
       </c>
       <c r="B95" t="n">
-        <v>0.01911938438686333</v>
+        <v>0.02755992888669309</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>745.884932411625</v>
+        <v>0.1966684910231475</v>
       </c>
       <c r="B96" t="n">
-        <v>0.02903599421017149</v>
+        <v>0.02407525123215008</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>753.8198785011103</v>
+        <v>0.1987607090127554</v>
       </c>
       <c r="B97" t="n">
-        <v>0.02031076614955117</v>
+        <v>0.02816312827424943</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>761.7548245905957</v>
+        <v>0.2008529270023634</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01181490703283877</v>
+        <v>0.02053623448450271</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>769.6897706800811</v>
+        <v>0.2029451449919713</v>
       </c>
       <c r="B99" t="n">
-        <v>0.004001429690467221</v>
+        <v>0.01840504921175447</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>777.6247167695665</v>
+        <v>0.2050373629815793</v>
       </c>
       <c r="B100" t="n">
-        <v>0.006101046930201631</v>
+        <v>0.01963964430466166</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>785.5596628590517</v>
+        <v>0.2071295809711872</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0186056510357759</v>
+        <v>0.02023361223791942</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>793.4946089485371</v>
+        <v>0.2092217989607952</v>
       </c>
       <c r="B102" t="n">
-        <v>0.0215632242022134</v>
+        <v>0.01382481373668053</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>801.4295550380225</v>
+        <v>0.2113140169504032</v>
       </c>
       <c r="B103" t="n">
-        <v>0.006377520381662671</v>
+        <v>0.02330355323250511</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>809.3645011275079</v>
+        <v>0.2134062349400111</v>
       </c>
       <c r="B104" t="n">
-        <v>0.006717903227963647</v>
+        <v>0.02569753533510052</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>817.2994472169933</v>
+        <v>0.2154984529296191</v>
       </c>
       <c r="B105" t="n">
-        <v>0.005005043514549538</v>
+        <v>0.01795555898112847</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>825.2343933064786</v>
+        <v>0.217590670919227</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0061095722611379</v>
+        <v>0.01350651160975986</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>833.169339395964</v>
+        <v>0.219682888908835</v>
       </c>
       <c r="B107" t="n">
-        <v>0.01590254158976446</v>
+        <v>0.003775310485569297</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>841.1042854854494</v>
+        <v>0.2217751068984429</v>
       </c>
       <c r="B108" t="n">
-        <v>0.01779773301603647</v>
+        <v>0.0115884174688655</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>849.0392315749348</v>
+        <v>0.2238673248880509</v>
       </c>
       <c r="B109" t="n">
-        <v>0.01497015286038235</v>
+        <v>0.02481059013673724</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>856.9741776644202</v>
+        <v>0.2259595428776588</v>
       </c>
       <c r="B110" t="n">
-        <v>0.01102780112560348</v>
+        <v>0.01622176099639604</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>864.9091237539055</v>
+        <v>0.2280517608672668</v>
       </c>
       <c r="B111" t="n">
-        <v>0.007862429643310204</v>
+        <v>0.009657549617774286</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>872.8440698433909</v>
+        <v>0.2301439788568747</v>
       </c>
       <c r="B112" t="n">
-        <v>0.01032547683113688</v>
+        <v>0.01038881011962561</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>880.7790159328763</v>
+        <v>0.2322361968464827</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0151190814768573</v>
+        <v>0.008606067320650458</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>888.7139620223617</v>
+        <v>0.2343284148360906</v>
       </c>
       <c r="B114" t="n">
-        <v>0.01112573838596423</v>
+        <v>0.01332929840205523</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>896.648908111847</v>
+        <v>0.2364206328256986</v>
       </c>
       <c r="B115" t="n">
-        <v>0.004951693798764892</v>
+        <v>0.02058528518065142</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>904.5838542013323</v>
+        <v>0.2385128508153065</v>
       </c>
       <c r="B116" t="n">
-        <v>0.005856314606131827</v>
+        <v>0.01463433733351605</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>912.5188002908177</v>
+        <v>0.2406050688049145</v>
       </c>
       <c r="B117" t="n">
-        <v>0.004812494574760861</v>
+        <v>0.004592468713934175</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>920.4537463803031</v>
+        <v>0.2426972867945224</v>
       </c>
       <c r="B118" t="n">
-        <v>0.001662603731829924</v>
+        <v>0.003168581099652774</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>928.3886924697885</v>
+        <v>0.2447895047841304</v>
       </c>
       <c r="B119" t="n">
-        <v>0.006323986782558381</v>
+        <v>0.005063978411911239</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>936.3236385592738</v>
+        <v>0.2468817227737383</v>
       </c>
       <c r="B120" t="n">
-        <v>0.01201643006875851</v>
+        <v>0.00796843099123031</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>944.2585846487592</v>
+        <v>0.2489739407633463</v>
       </c>
       <c r="B121" t="n">
-        <v>0.01750896565785004</v>
+        <v>0.002195856557027745</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>952.1935307382446</v>
+        <v>0.2510661587529542</v>
       </c>
       <c r="B122" t="n">
-        <v>0.0163293670579844</v>
+        <v>0.01003336855462469</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>960.12847682773</v>
+        <v>0.2531583767425622</v>
       </c>
       <c r="B123" t="n">
-        <v>0.008925684371963553</v>
+        <v>0.02083098328355852</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>968.0634229172153</v>
+        <v>0.2552505947321702</v>
       </c>
       <c r="B124" t="n">
-        <v>0.007585699023462876</v>
+        <v>0.02010980649530458</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>975.9983690067007</v>
+        <v>0.2573428127217781</v>
       </c>
       <c r="B125" t="n">
-        <v>0.002194178777111184</v>
+        <v>0.006266190656424844</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>983.9333150961861</v>
+        <v>0.2594350307113861</v>
       </c>
       <c r="B126" t="n">
-        <v>0.008416428641540952</v>
+        <v>0.006016741202231074</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>991.8682611856715</v>
+        <v>0.261527248700994</v>
       </c>
       <c r="B127" t="n">
-        <v>0.004174143549204838</v>
+        <v>0.01386505352584018</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>999.8032072751569</v>
+        <v>0.2636194666906019</v>
       </c>
       <c r="B128" t="n">
-        <v>0.01221645237261734</v>
+        <v>0.02330196322653062</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1007.738153364642</v>
+        <v>0.2657116846802099</v>
       </c>
       <c r="B129" t="n">
-        <v>0.006729511475366727</v>
+        <v>0.01540435842775452</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1015.673099454128</v>
+        <v>0.2678039026698179</v>
       </c>
       <c r="B130" t="n">
-        <v>0.01077464635442761</v>
+        <v>0.006860694028966991</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1023.608045543613</v>
+        <v>0.2698961206594258</v>
       </c>
       <c r="B131" t="n">
-        <v>0.01368185858600899</v>
+        <v>0.006082206456806307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1031.542991633098</v>
+        <v>0.2719883386490338</v>
       </c>
       <c r="B132" t="n">
-        <v>0.005059116842606457</v>
+        <v>0.006907936214848207</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1039.477937722584</v>
+        <v>0.2740805566386417</v>
       </c>
       <c r="B133" t="n">
-        <v>0.008022955117484132</v>
+        <v>0.006009469888120546</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1047.412883812069</v>
+        <v>0.2761727746282497</v>
       </c>
       <c r="B134" t="n">
-        <v>0.009791136853552526</v>
+        <v>0.003967249926154876</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1055.347829901554</v>
+        <v>0.2782649926178576</v>
       </c>
       <c r="B135" t="n">
-        <v>0.008933003084704155</v>
+        <v>0.0104918990861548</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1063.28277599104</v>
+        <v>0.2803572106074655</v>
       </c>
       <c r="B136" t="n">
-        <v>0.009796091473163895</v>
+        <v>0.0139814288894412</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1071.217722080525</v>
+        <v>0.2824494285970735</v>
       </c>
       <c r="B137" t="n">
-        <v>0.007620937895405395</v>
+        <v>0.00806098356538743</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1079.152668170011</v>
+        <v>0.2845416465866815</v>
       </c>
       <c r="B138" t="n">
-        <v>0.01168449899090231</v>
+        <v>0.02433004588734412</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1087.087614259496</v>
+        <v>0.2866338645762894</v>
       </c>
       <c r="B139" t="n">
-        <v>0.007863810187131375</v>
+        <v>0.02373380118241729</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1095.022560348981</v>
+        <v>0.2887260825658974</v>
       </c>
       <c r="B140" t="n">
-        <v>0.008551471696266365</v>
+        <v>0.008841059897829089</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1102.957506438467</v>
+        <v>0.2908183005555053</v>
       </c>
       <c r="B141" t="n">
-        <v>0.005214807422970738</v>
+        <v>0.005575440312259602</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1110.892452527952</v>
+        <v>0.2929105185451133</v>
       </c>
       <c r="B142" t="n">
-        <v>0.006807122764452436</v>
+        <v>0.00384377231428294</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1118.827398617437</v>
+        <v>0.2950027365347213</v>
       </c>
       <c r="B143" t="n">
-        <v>0.00930423387962917</v>
+        <v>0.01138296169062236</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1126.762344706923</v>
+        <v>0.2970949545243292</v>
       </c>
       <c r="B144" t="n">
-        <v>0.005588058469046309</v>
+        <v>0.007413771281422336</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1134.697290796408</v>
+        <v>0.2991871725139371</v>
       </c>
       <c r="B145" t="n">
-        <v>0.01767130449047731</v>
+        <v>0.004838301553185879</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1142.632236885893</v>
+        <v>0.3012793905035451</v>
       </c>
       <c r="B146" t="n">
-        <v>0.01636725073244061</v>
+        <v>0.003367695783278317</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1150.567182975379</v>
+        <v>0.303371608493153</v>
       </c>
       <c r="B147" t="n">
-        <v>0.0124136979156912</v>
+        <v>0.006715687989227676</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1158.502129064864</v>
+        <v>0.305463826482761</v>
       </c>
       <c r="B148" t="n">
-        <v>0.004509284037597585</v>
+        <v>0.01400188105842211</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1166.43707515435</v>
+        <v>0.307556044472369</v>
       </c>
       <c r="B149" t="n">
-        <v>0.01220127082525192</v>
+        <v>0.01396531648540765</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1174.372021243835</v>
+        <v>0.3096482624619769</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0111631288770224</v>
+        <v>0.00793226709951983</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1182.30696733332</v>
+        <v>0.3117404804515849</v>
       </c>
       <c r="B151" t="n">
-        <v>0.0101000417706644</v>
+        <v>0.008111474902861482</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1190.241913422806</v>
+        <v>0.3138326984411928</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0164033652742941</v>
+        <v>0.01002359606299413</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1198.176859512291</v>
+        <v>0.3159249164308007</v>
       </c>
       <c r="B153" t="n">
-        <v>0.007263723645964216</v>
+        <v>0.00653195580432625</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1206.111805601776</v>
+        <v>0.3180171344204087</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0104476896207655</v>
+        <v>0.00569412265763851</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1214.046751691262</v>
+        <v>0.3201093524100166</v>
       </c>
       <c r="B155" t="n">
-        <v>0.02120948653782721</v>
+        <v>0.004293216060133087</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1221.981697780747</v>
+        <v>0.3222015703996246</v>
       </c>
       <c r="B156" t="n">
-        <v>0.01504675451418237</v>
+        <v>0.01003321162021943</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1229.916643870233</v>
+        <v>0.3242937883892326</v>
       </c>
       <c r="B157" t="n">
-        <v>0.005525853854597796</v>
+        <v>0.007172278194101125</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1237.851589959718</v>
+        <v>0.3263860063788405</v>
       </c>
       <c r="B158" t="n">
-        <v>0.01130798975759824</v>
+        <v>0.01003364370766488</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1245.786536049203</v>
+        <v>0.3284782243684485</v>
       </c>
       <c r="B159" t="n">
-        <v>0.02016794614474713</v>
+        <v>0.0119877225726904</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1253.721482138689</v>
+        <v>0.3305704423580564</v>
       </c>
       <c r="B160" t="n">
-        <v>0.02208792337359561</v>
+        <v>0.01569586583247685</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1261.656428228174</v>
+        <v>0.3326626603476644</v>
       </c>
       <c r="B161" t="n">
-        <v>0.01458426499614731</v>
+        <v>0.009819864412226161</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1269.59137431766</v>
+        <v>0.3347548783372723</v>
       </c>
       <c r="B162" t="n">
-        <v>0.01215119669538102</v>
+        <v>0.01283064988361943</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1277.526320407145</v>
+        <v>0.3368470963268803</v>
       </c>
       <c r="B163" t="n">
-        <v>0.01231223843544362</v>
+        <v>0.01424671721173718</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1285.46126649663</v>
+        <v>0.3389393143164882</v>
       </c>
       <c r="B164" t="n">
-        <v>0.002985235024336825</v>
+        <v>0.007518149880726397</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1293.396212586116</v>
+        <v>0.3410315323060962</v>
       </c>
       <c r="B165" t="n">
-        <v>0.01429191936961682</v>
+        <v>0.01593370460933686</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1301.331158675601</v>
+        <v>0.3431237502957041</v>
       </c>
       <c r="B166" t="n">
-        <v>0.01147611787670555</v>
+        <v>0.0178892448726381</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1309.266104765086</v>
+        <v>0.3452159682853121</v>
       </c>
       <c r="B167" t="n">
-        <v>0.005933303665133135</v>
+        <v>0.02032588894783102</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1317.201050854572</v>
+        <v>0.34730818627492</v>
       </c>
       <c r="B168" t="n">
-        <v>0.01202109568238609</v>
+        <v>0.01392769881240783</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1325.135996944057</v>
+        <v>0.349400404264528</v>
       </c>
       <c r="B169" t="n">
-        <v>0.01095701799269848</v>
+        <v>0.01157614022149185</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1333.070943033542</v>
+        <v>0.3514926222541359</v>
       </c>
       <c r="B170" t="n">
-        <v>0.01022962169414402</v>
+        <v>0.007714083063889439</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1341.005889123028</v>
+        <v>0.3535848402437439</v>
       </c>
       <c r="B171" t="n">
-        <v>0.01650497727137896</v>
+        <v>0.008454160270078639</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1348.940835212513</v>
+        <v>0.3556770582333518</v>
       </c>
       <c r="B172" t="n">
-        <v>0.01140120792735088</v>
+        <v>0.02124579784985583</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1356.875781301999</v>
+        <v>0.3577692762229598</v>
       </c>
       <c r="B173" t="n">
-        <v>0.006439271132157005</v>
+        <v>0.01639226069668219</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1364.810727391484</v>
+        <v>0.3598614942125677</v>
       </c>
       <c r="B174" t="n">
-        <v>0.009794715454379387</v>
+        <v>0.01364818478552094</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1372.745673480969</v>
+        <v>0.3619537122021757</v>
       </c>
       <c r="B175" t="n">
-        <v>0.004501738879507966</v>
+        <v>0.01117818871148408</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1380.680619570455</v>
+        <v>0.3640459301917837</v>
       </c>
       <c r="B176" t="n">
-        <v>0.003976857484300739</v>
+        <v>0.01799784934533362</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1388.61556565994</v>
+        <v>0.3661381481813916</v>
       </c>
       <c r="B177" t="n">
-        <v>0.007059796420326085</v>
+        <v>0.01924897946569757</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1396.550511749425</v>
+        <v>0.3682303661709996</v>
       </c>
       <c r="B178" t="n">
-        <v>0.007083532953312949</v>
+        <v>0.01791416450624912</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1404.485457838911</v>
+        <v>0.3703225841606075</v>
       </c>
       <c r="B179" t="n">
-        <v>0.01123299847792407</v>
+        <v>0.02117292496569729</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1412.420403928396</v>
+        <v>0.3724148021502154</v>
       </c>
       <c r="B180" t="n">
-        <v>0.01524505922972323</v>
+        <v>0.02822293957545097</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1420.355350017882</v>
+        <v>0.3745070201398234</v>
       </c>
       <c r="B181" t="n">
-        <v>0.01119387481972782</v>
+        <v>0.0205226454052221</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1428.290296107367</v>
+        <v>0.3765992381294314</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0144559429599383</v>
+        <v>0.001317356922445243</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1436.225242196852</v>
+        <v>0.3786914561190393</v>
       </c>
       <c r="B183" t="n">
-        <v>0.01162840056134274</v>
+        <v>0.007030161000942463</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1444.160188286338</v>
+        <v>0.3807836741086473</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0198589122960979</v>
+        <v>0.01112146735610478</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1452.095134375823</v>
+        <v>0.3828758920982552</v>
       </c>
       <c r="B185" t="n">
-        <v>0.01089867868636117</v>
+        <v>0.00599484766948813</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1460.030080465308</v>
+        <v>0.3849681100878632</v>
       </c>
       <c r="B186" t="n">
-        <v>0.01495031142573895</v>
+        <v>0.006689083172498275</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1467.965026554794</v>
+        <v>0.3870603280774711</v>
       </c>
       <c r="B187" t="n">
-        <v>0.01717839408652223</v>
+        <v>0.01578656055069383</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1475.899972644279</v>
+        <v>0.3891525460670791</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0239278932964461</v>
+        <v>0.01719455010361961</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1483.834918733764</v>
+        <v>0.391244764056687</v>
       </c>
       <c r="B189" t="n">
-        <v>0.02047867205937525</v>
+        <v>0.007033247421311266</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1491.76986482325</v>
+        <v>0.393336982046295</v>
       </c>
       <c r="B190" t="n">
-        <v>0.01323221629568363</v>
+        <v>0.01088858453140007</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1499.704810912735</v>
+        <v>0.3954292000359029</v>
       </c>
       <c r="B191" t="n">
-        <v>0.01432323555748113</v>
+        <v>0.01207516491670062</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1507.639757002221</v>
+        <v>0.3975214180255109</v>
       </c>
       <c r="B192" t="n">
-        <v>0.009605934540939968</v>
+        <v>0.009218960175796752</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1515.574703091706</v>
+        <v>0.3996136360151188</v>
       </c>
       <c r="B193" t="n">
-        <v>0.01132219417300011</v>
+        <v>0.01065005671424346</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1523.509649181191</v>
+        <v>0.4017058540047268</v>
       </c>
       <c r="B194" t="n">
-        <v>0.02034106191698912</v>
+        <v>0.02253717056687808</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1531.444595270677</v>
+        <v>0.4037980719943348</v>
       </c>
       <c r="B195" t="n">
-        <v>0.01605352962308465</v>
+        <v>0.02196824585902151</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1539.379541360162</v>
+        <v>0.4058902899839427</v>
       </c>
       <c r="B196" t="n">
-        <v>0.004063511923024095</v>
+        <v>0.01550011375723421</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1547.314487449647</v>
+        <v>0.4079825079735506</v>
       </c>
       <c r="B197" t="n">
-        <v>0.02333448599987631</v>
+        <v>0.003109273054102549</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1555.249433539133</v>
+        <v>0.4100747259631586</v>
       </c>
       <c r="B198" t="n">
-        <v>0.03254162438955656</v>
+        <v>0.006409953572315303</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1563.184379628618</v>
+        <v>0.4121669439527665</v>
       </c>
       <c r="B199" t="n">
-        <v>0.01869128312680311</v>
+        <v>0.01571820822251206</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1571.119325718103</v>
+        <v>0.4142591619423745</v>
       </c>
       <c r="B200" t="n">
-        <v>0.01432050837254231</v>
+        <v>0.001137544798109601</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1579.054271807589</v>
+        <v>0.4163513799319825</v>
       </c>
       <c r="B201" t="n">
-        <v>0.01639308430985511</v>
+        <v>0.01062974619608173</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1586.989217897074</v>
+        <v>0.4184435979215904</v>
       </c>
       <c r="B202" t="n">
-        <v>0.006204475141473965</v>
+        <v>0.006669522372723619</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1594.92416398656</v>
+        <v>0.4205358159111984</v>
       </c>
       <c r="B203" t="n">
-        <v>0.009575174669194542</v>
+        <v>0.004756970810269831</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1602.859110076045</v>
+        <v>0.4226280339008063</v>
       </c>
       <c r="B204" t="n">
-        <v>0.02052820105872401</v>
+        <v>0.007744436418350011</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1610.79405616553</v>
+        <v>0.4247202518904142</v>
       </c>
       <c r="B205" t="n">
-        <v>0.01591307692111781</v>
+        <v>0.01252631328207364</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1618.729002255016</v>
+        <v>0.4268124698800222</v>
       </c>
       <c r="B206" t="n">
-        <v>0.006051403800487307</v>
+        <v>0.005810281196320243</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1626.663948344501</v>
+        <v>0.4289046878696302</v>
       </c>
       <c r="B207" t="n">
-        <v>0.0104377258266848</v>
+        <v>0.01409702886045576</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1634.598894433987</v>
+        <v>0.4309969058592381</v>
       </c>
       <c r="B208" t="n">
-        <v>0.01163438537138253</v>
+        <v>0.01338013961816463</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1642.533840523472</v>
+        <v>0.4330891238488461</v>
       </c>
       <c r="B209" t="n">
-        <v>0.001533448880811847</v>
+        <v>0.01760523558493665</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1650.468786612957</v>
+        <v>0.435181341838454</v>
       </c>
       <c r="B210" t="n">
-        <v>0.005233610642408691</v>
+        <v>0.01309880240308382</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1658.403732702443</v>
+        <v>0.437273559828062</v>
       </c>
       <c r="B211" t="n">
-        <v>0.01510400275557336</v>
+        <v>0.006493374042122298</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1666.338678791928</v>
+        <v>0.4393657778176699</v>
       </c>
       <c r="B212" t="n">
-        <v>0.004919256836827323</v>
+        <v>0.01801677021605893</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1674.273624881414</v>
+        <v>0.4414579958072779</v>
       </c>
       <c r="B213" t="n">
-        <v>0.007874033579372648</v>
+        <v>0.02718335958007985</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1682.208570970899</v>
+        <v>0.4435502137968858</v>
       </c>
       <c r="B214" t="n">
-        <v>0.01989451951669637</v>
+        <v>0.03018905055566483</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1690.143517060384</v>
+        <v>0.4456424317864938</v>
       </c>
       <c r="B215" t="n">
-        <v>0.02415282184300171</v>
+        <v>0.02563337958446737</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1698.07846314987</v>
+        <v>0.4477346497761017</v>
       </c>
       <c r="B216" t="n">
-        <v>0.02698645759201306</v>
+        <v>0.008609996436126947</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1706.013409239355</v>
+        <v>0.4498268677657097</v>
       </c>
       <c r="B217" t="n">
-        <v>0.02489906653683157</v>
+        <v>0.0143537252837564</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1713.94835532884</v>
+        <v>0.4519190857553176</v>
       </c>
       <c r="B218" t="n">
-        <v>0.01542478794050497</v>
+        <v>0.010447608001615</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1721.883301418326</v>
+        <v>0.4540113037449256</v>
       </c>
       <c r="B219" t="n">
-        <v>0.008790042331543395</v>
+        <v>0.004079566953738741</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1729.818247507811</v>
+        <v>0.4561035217345336</v>
       </c>
       <c r="B220" t="n">
-        <v>0.00929214708077503</v>
+        <v>0.01870587593247017</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1737.753193597296</v>
+        <v>0.4581957397241415</v>
       </c>
       <c r="B221" t="n">
-        <v>0.015531893588334</v>
+        <v>0.01717314705290146</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1745.688139686782</v>
+        <v>0.4602879577137494</v>
       </c>
       <c r="B222" t="n">
-        <v>0.008503678403310167</v>
+        <v>0.01032554704301786</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1753.623085776267</v>
+        <v>0.4623801757033574</v>
       </c>
       <c r="B223" t="n">
-        <v>0.02090922701151438</v>
+        <v>0.01537888901991834</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1761.558031865753</v>
+        <v>0.4644723936929653</v>
       </c>
       <c r="B224" t="n">
-        <v>0.03139484841640125</v>
+        <v>0.01167591260667251</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1769.492977955238</v>
+        <v>0.4665646116825733</v>
       </c>
       <c r="B225" t="n">
-        <v>0.01567891191693335</v>
+        <v>0.01516038915106173</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1777.427924044723</v>
+        <v>0.4686568296721813</v>
       </c>
       <c r="B226" t="n">
-        <v>0.007399520212196041</v>
+        <v>0.01205815285116085</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1785.362870134209</v>
+        <v>0.4707490476617892</v>
       </c>
       <c r="B227" t="n">
-        <v>0.006708903372694593</v>
+        <v>0.01024275597938316</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1793.297816223694</v>
+        <v>0.4728412656513972</v>
       </c>
       <c r="B228" t="n">
-        <v>0.003670096946743776</v>
+        <v>0.005580308655237413</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1801.232762313179</v>
+        <v>0.4749334836410051</v>
       </c>
       <c r="B229" t="n">
-        <v>0.00294598638564935</v>
+        <v>0.01171267187916438</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1809.167708402665</v>
+        <v>0.4770257016306131</v>
       </c>
       <c r="B230" t="n">
-        <v>0.006957568095143949</v>
+        <v>0.004610199011773542</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1817.10265449215</v>
+        <v>0.479117919620221</v>
       </c>
       <c r="B231" t="n">
-        <v>0.006233583253441747</v>
+        <v>0.01370490933479291</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1825.037600581635</v>
+        <v>0.4812101376098289</v>
       </c>
       <c r="B232" t="n">
-        <v>0.004953670699517372</v>
+        <v>0.009017941932967831</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1832.972546671121</v>
+        <v>0.4833023555994369</v>
       </c>
       <c r="B233" t="n">
-        <v>0.01563742917768867</v>
+        <v>0.005987213029103084</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1840.907492760606</v>
+        <v>0.4853945735890449</v>
       </c>
       <c r="B234" t="n">
-        <v>0.01026804729063033</v>
+        <v>0.008088617261719279</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1848.842438850092</v>
+        <v>0.4874867915786528</v>
       </c>
       <c r="B235" t="n">
-        <v>0.01242792129021565</v>
+        <v>0.01304632168772832</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1856.777384939577</v>
+        <v>0.4895790095682608</v>
       </c>
       <c r="B236" t="n">
-        <v>0.01523868456797737</v>
+        <v>0.02130080756903739</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1864.712331029062</v>
+        <v>0.4916712275578687</v>
       </c>
       <c r="B237" t="n">
-        <v>0.01104059642659304</v>
+        <v>0.01370270375927083</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1872.647277118548</v>
+        <v>0.4937634455474767</v>
       </c>
       <c r="B238" t="n">
-        <v>0.01226401640692211</v>
+        <v>0.004194188805907155</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1880.582223208033</v>
+        <v>0.4958556635370846</v>
       </c>
       <c r="B239" t="n">
-        <v>0.01213126067084722</v>
+        <v>0.01994338893992244</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1888.517169297518</v>
+        <v>0.4979478815266926</v>
       </c>
       <c r="B240" t="n">
-        <v>0.01197245292592638</v>
+        <v>0.03355547502635516</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1896.452115387004</v>
+        <v>0.5000400995163006</v>
       </c>
       <c r="B241" t="n">
-        <v>0.01631922815634741</v>
+        <v>0.004229499579904018</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1904.387061476489</v>
+        <v>0.5021323175059085</v>
       </c>
       <c r="B242" t="n">
-        <v>0.03099766722693167</v>
+        <v>0.01694429492888025</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1912.322007565975</v>
+        <v>0.5042245354955165</v>
       </c>
       <c r="B243" t="n">
-        <v>0.01823420034561314</v>
+        <v>0.02943637560200212</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1920.25695365546</v>
+        <v>0.5063167534851244</v>
       </c>
       <c r="B244" t="n">
-        <v>0.02421605885559438</v>
+        <v>0.01820735818739126</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1928.191899744945</v>
+        <v>0.5084089714747323</v>
       </c>
       <c r="B245" t="n">
-        <v>0.004152800792241659</v>
+        <v>0.01466039824383158</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1936.126845834431</v>
+        <v>0.5105011894643403</v>
       </c>
       <c r="B246" t="n">
-        <v>0.009739344183944246</v>
+        <v>0.01789129972875621</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1944.061791923916</v>
+        <v>0.5125934074539482</v>
       </c>
       <c r="B247" t="n">
-        <v>0.01231981522920639</v>
+        <v>0.005904721392303441</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1951.996738013401</v>
+        <v>0.5146856254435562</v>
       </c>
       <c r="B248" t="n">
-        <v>0.01329874520427865</v>
+        <v>0.005832214602321487</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1959.931684102887</v>
+        <v>0.5167778434331641</v>
       </c>
       <c r="B249" t="n">
-        <v>0.0203587095499254</v>
+        <v>0.006435927148658531</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1967.866630192372</v>
+        <v>0.5188700614227721</v>
       </c>
       <c r="B250" t="n">
-        <v>0.02798849718387016</v>
+        <v>0.0190151222987471</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1975.801576281857</v>
+        <v>0.52096227941238</v>
       </c>
       <c r="B251" t="n">
-        <v>0.01828474422526324</v>
+        <v>0.01397020530879866</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1983.736522371343</v>
+        <v>0.523054497401988</v>
       </c>
       <c r="B252" t="n">
-        <v>0.01218500734116964</v>
+        <v>0.01260895411528404</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1991.671468460828</v>
+        <v>0.525146715391596</v>
       </c>
       <c r="B253" t="n">
-        <v>0.006976186634347872</v>
+        <v>0.01008122091456728</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1999.606414550314</v>
+        <v>0.5272389333812039</v>
       </c>
       <c r="B254" t="n">
-        <v>0.01023732607827568</v>
+        <v>0.02376176559566626</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2007.541360639799</v>
+        <v>0.5293311513708119</v>
       </c>
       <c r="B255" t="n">
-        <v>0.007892555849391365</v>
+        <v>0.01593029384635438</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2015.476306729284</v>
+        <v>0.5314233693604198</v>
       </c>
       <c r="B256" t="n">
-        <v>0.02443530724342282</v>
+        <v>0.004415122241576776</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2023.41125281877</v>
+        <v>0.5335155873500278</v>
       </c>
       <c r="B257" t="n">
-        <v>0.01434484220179737</v>
+        <v>0.01575295348278562</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2031.346198908255</v>
+        <v>0.5356078053396357</v>
       </c>
       <c r="B258" t="n">
-        <v>0.003109673414624475</v>
+        <v>0.01255743733710905</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2039.281144997741</v>
+        <v>0.5377000233292437</v>
       </c>
       <c r="B259" t="n">
-        <v>0.00837806830726338</v>
+        <v>0.01617441808421589</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2047.216091087226</v>
+        <v>0.5397922413188516</v>
       </c>
       <c r="B260" t="n">
-        <v>0.0109160304247857</v>
+        <v>0.02441624850674337</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2055.151037176711</v>
+        <v>0.5418844593084595</v>
       </c>
       <c r="B261" t="n">
-        <v>0.01473812319323452</v>
+        <v>0.02036462111803769</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2063.085983266197</v>
+        <v>0.5439766772980675</v>
       </c>
       <c r="B262" t="n">
-        <v>0.02709372857241083</v>
+        <v>0.01698468408604142</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2071.020929355682</v>
+        <v>0.5460688952876754</v>
       </c>
       <c r="B263" t="n">
-        <v>0.01819453779691812</v>
+        <v>0.01876941835926972</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2078.955875445167</v>
+        <v>0.5481611132772835</v>
       </c>
       <c r="B264" t="n">
-        <v>0.007335678502439126</v>
+        <v>0.03710476814180949</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2086.890821534653</v>
+        <v>0.5502533312668914</v>
       </c>
       <c r="B265" t="n">
-        <v>0.00991604659349506</v>
+        <v>0.03442341555232513</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2094.825767624138</v>
+        <v>0.5523455492564994</v>
       </c>
       <c r="B266" t="n">
-        <v>0.005180754209548385</v>
+        <v>0.01444435357818012</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2102.760713713623</v>
+        <v>0.5544377672461073</v>
       </c>
       <c r="B267" t="n">
-        <v>0.003386539680507593</v>
+        <v>0.01687823220302468</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2110.695659803109</v>
+        <v>0.5565299852357153</v>
       </c>
       <c r="B268" t="n">
-        <v>0.01852664172757557</v>
+        <v>0.0281875395953653</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2118.630605892594</v>
+        <v>0.5586222032253232</v>
       </c>
       <c r="B269" t="n">
-        <v>0.01520399413593637</v>
+        <v>0.02084100650223641</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2126.56555198208</v>
+        <v>0.5607144212149311</v>
       </c>
       <c r="B270" t="n">
-        <v>0.004921468744927956</v>
+        <v>0.005026202386150967</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2134.500498071565</v>
+        <v>0.5628066392045391</v>
       </c>
       <c r="B271" t="n">
-        <v>0.01370188697016894</v>
+        <v>0.01799204563763134</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2142.43544416105</v>
+        <v>0.564898857194147</v>
       </c>
       <c r="B272" t="n">
-        <v>0.02126354291157802</v>
+        <v>0.01389127636205177</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2150.370390250536</v>
+        <v>0.566991075183755</v>
       </c>
       <c r="B273" t="n">
-        <v>0.006918330725440274</v>
+        <v>0.01089159245442214</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2158.305336340021</v>
+        <v>0.5690832931733629</v>
       </c>
       <c r="B274" t="n">
-        <v>0.01534322996037367</v>
+        <v>0.0100262549945629</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2166.240282429506</v>
+        <v>0.5711755111629709</v>
       </c>
       <c r="B275" t="n">
-        <v>0.02253464629825056</v>
+        <v>0.02144743850328715</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2174.175228518992</v>
+        <v>0.5732677291525788</v>
       </c>
       <c r="B276" t="n">
-        <v>0.02309285365510919</v>
+        <v>0.01491644345852398</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2182.110174608477</v>
+        <v>0.5753599471421869</v>
       </c>
       <c r="B277" t="n">
-        <v>0.007527545835365332</v>
+        <v>0.03137261094796415</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2190.045120697962</v>
+        <v>0.5774521651317948</v>
       </c>
       <c r="B278" t="n">
-        <v>0.009378431090627139</v>
+        <v>0.02200086682119746</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2197.980066787448</v>
+        <v>0.5795443831214027</v>
       </c>
       <c r="B279" t="n">
-        <v>0.01526623152911418</v>
+        <v>0.004421719537648651</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2205.915012876933</v>
+        <v>0.5816366011110107</v>
       </c>
       <c r="B280" t="n">
-        <v>0.02422297342165877</v>
+        <v>0.01702976262661524</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2213.849958966419</v>
+        <v>0.5837288191006186</v>
       </c>
       <c r="B281" t="n">
-        <v>0.02076915910479819</v>
+        <v>0.02015061290918581</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2221.784905055904</v>
+        <v>0.5858210370902266</v>
       </c>
       <c r="B282" t="n">
-        <v>0.02233809300800736</v>
+        <v>0.01829330336748445</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2229.719851145389</v>
+        <v>0.5879132550798345</v>
       </c>
       <c r="B283" t="n">
-        <v>0.02871669114370264</v>
+        <v>0.02102203788782121</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2237.654797234875</v>
+        <v>0.5900054730694425</v>
       </c>
       <c r="B284" t="n">
-        <v>0.03614532500096988</v>
+        <v>0.0266573485134052</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2245.58974332436</v>
+        <v>0.5920976910590504</v>
       </c>
       <c r="B285" t="n">
-        <v>0.0289083832679981</v>
+        <v>0.0226513160222838</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2253.524689413845</v>
+        <v>0.5941899090486584</v>
       </c>
       <c r="B286" t="n">
-        <v>0.01347414307099401</v>
+        <v>0.02803298176927614</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2261.459635503331</v>
+        <v>0.5962821270382663</v>
       </c>
       <c r="B287" t="n">
-        <v>0.02014894215512182</v>
+        <v>0.01284336759551001</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2269.394581592816</v>
+        <v>0.5983743450278742</v>
       </c>
       <c r="B288" t="n">
-        <v>0.01058100192426153</v>
+        <v>0.01348257525251766</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2277.329527682302</v>
+        <v>0.6004665630174822</v>
       </c>
       <c r="B289" t="n">
-        <v>0.01541682931226712</v>
+        <v>0.0319103720625805</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2285.264473771787</v>
+        <v>0.6025587810070901</v>
       </c>
       <c r="B290" t="n">
-        <v>0.005810333585746186</v>
+        <v>0.01094258627563206</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2293.199419861272</v>
+        <v>0.6046509989966982</v>
       </c>
       <c r="B291" t="n">
-        <v>0.01236986828923092</v>
+        <v>0.03012920779492248</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2301.134365950758</v>
+        <v>0.6067432169863061</v>
       </c>
       <c r="B292" t="n">
-        <v>0.007900488319742395</v>
+        <v>0.01758685918829049</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2309.069312040243</v>
+        <v>0.6088354349759141</v>
       </c>
       <c r="B293" t="n">
-        <v>0.01406570762045198</v>
+        <v>0.01424542944948419</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2317.004258129728</v>
+        <v>0.610927652965522</v>
       </c>
       <c r="B294" t="n">
-        <v>0.01215478306015336</v>
+        <v>0.02334825648235677</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2324.939204219214</v>
+        <v>0.6130198709551299</v>
       </c>
       <c r="B295" t="n">
-        <v>0.008378494303530286</v>
+        <v>0.02352457165422078</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2332.874150308699</v>
+        <v>0.6151120889447379</v>
       </c>
       <c r="B296" t="n">
-        <v>0.01919415865008845</v>
+        <v>0.01841739259401003</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2340.809096398184</v>
+        <v>0.6172043069343458</v>
       </c>
       <c r="B297" t="n">
-        <v>0.01681781495449706</v>
+        <v>0.003823078503865485</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2348.74404248767</v>
+        <v>0.6192965249239538</v>
       </c>
       <c r="B298" t="n">
-        <v>0.01226119815359652</v>
+        <v>0.03417541520606402</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2356.678988577155</v>
+        <v>0.6213887429135617</v>
       </c>
       <c r="B299" t="n">
-        <v>0.01221042739627421</v>
+        <v>0.02089407219644216</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2364.613934666641</v>
+        <v>0.6234809609031697</v>
       </c>
       <c r="B300" t="n">
-        <v>0.02673848198014224</v>
+        <v>0.009013204797159969</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2372.548880756126</v>
+        <v>0.6255731788927776</v>
       </c>
       <c r="B301" t="n">
-        <v>0.022839103497086</v>
+        <v>0.01461160887768237</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2380.483826845611</v>
+        <v>0.6276653968823857</v>
       </c>
       <c r="B302" t="n">
-        <v>0.02995006429674834</v>
+        <v>0.01550958446649796</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2388.418772935097</v>
+        <v>0.6297576148719936</v>
       </c>
       <c r="B303" t="n">
-        <v>0.01461878305215251</v>
+        <v>0.009544669389430816</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2396.353719024582</v>
+        <v>0.6318498328616015</v>
       </c>
       <c r="B304" t="n">
-        <v>0.01306957107587672</v>
+        <v>0.004829013915226937</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2404.288665114067</v>
+        <v>0.6339420508512095</v>
       </c>
       <c r="B305" t="n">
-        <v>0.001860067448033049</v>
+        <v>0.00994916238307272</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2412.223611203553</v>
+        <v>0.6360342688408174</v>
       </c>
       <c r="B306" t="n">
-        <v>0.01813220696989694</v>
+        <v>0.006670644581768096</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2420.158557293038</v>
+        <v>0.6381264868304254</v>
       </c>
       <c r="B307" t="n">
-        <v>0.01072550319113613</v>
+        <v>0.008966689542859339</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2428.093503382524</v>
+        <v>0.6402187048200333</v>
       </c>
       <c r="B308" t="n">
-        <v>0.01278875843878477</v>
+        <v>0.01589799558661129</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2436.028449472009</v>
+        <v>0.6423109228096413</v>
       </c>
       <c r="B309" t="n">
-        <v>0.01141576317210608</v>
+        <v>0.01661947722988118</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2443.963395561495</v>
+        <v>0.6444031407992492</v>
       </c>
       <c r="B310" t="n">
-        <v>0.002357927483832145</v>
+        <v>0.009001528117494781</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2451.89834165098</v>
+        <v>0.6464953587888572</v>
       </c>
       <c r="B311" t="n">
-        <v>0.01850577466666083</v>
+        <v>0.01782768869283006</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2459.833287740465</v>
+        <v>0.6485875767784651</v>
       </c>
       <c r="B312" t="n">
-        <v>0.01212406485678204</v>
+        <v>0.02392505087640861</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2467.768233829951</v>
+        <v>0.650679794768073</v>
       </c>
       <c r="B313" t="n">
-        <v>0.01196074313979021</v>
+        <v>0.0216896029121277</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2475.703179919436</v>
+        <v>0.652772012757681</v>
       </c>
       <c r="B314" t="n">
-        <v>0.01579359238661986</v>
+        <v>0.01240407103129661</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2483.638126008922</v>
+        <v>0.6548642307472889</v>
       </c>
       <c r="B315" t="n">
-        <v>0.007486030097370204</v>
+        <v>0.01715998263578551</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2491.573072098407</v>
+        <v>0.656956448736897</v>
       </c>
       <c r="B316" t="n">
-        <v>0.01642399688915706</v>
+        <v>0.02146213008951012</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2499.508018187892</v>
+        <v>0.6590486667265049</v>
       </c>
       <c r="B317" t="n">
-        <v>0.02132201770571368</v>
+        <v>0.003834044562009916</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2507.442964277378</v>
+        <v>0.6611408847161129</v>
       </c>
       <c r="B318" t="n">
-        <v>0.01074827980718864</v>
+        <v>0.0183816778101173</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2515.377910366863</v>
+        <v>0.6632331027057208</v>
       </c>
       <c r="B319" t="n">
-        <v>0.001848803254653495</v>
+        <v>0.01506695049879259</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2523.312856456348</v>
+        <v>0.6653253206953288</v>
       </c>
       <c r="B320" t="n">
-        <v>0.01456809515748548</v>
+        <v>0.0101169547134122</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2531.247802545834</v>
+        <v>0.6674175386849367</v>
       </c>
       <c r="B321" t="n">
-        <v>0.01993975351434161</v>
+        <v>0.009001289035360802</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2539.182748635319</v>
+        <v>0.6695097566745446</v>
       </c>
       <c r="B322" t="n">
-        <v>0.01080826674454657</v>
+        <v>0.01092447461019327</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2547.117694724804</v>
+        <v>0.6716019746641526</v>
       </c>
       <c r="B323" t="n">
-        <v>0.00591809063397166</v>
+        <v>0.01381639158696615</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2555.05264081429</v>
+        <v>0.6736941926537605</v>
       </c>
       <c r="B324" t="n">
-        <v>0.01251247896553919</v>
+        <v>0.009552606478721967</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2562.987586903775</v>
+        <v>0.6757864106433685</v>
       </c>
       <c r="B325" t="n">
-        <v>0.01061102663576994</v>
+        <v>0.02063535167254817</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2570.922532993261</v>
+        <v>0.6778786286329764</v>
       </c>
       <c r="B326" t="n">
-        <v>0.005407111990762732</v>
+        <v>0.01238706205389078</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2578.857479082746</v>
+        <v>0.6799708466225844</v>
       </c>
       <c r="B327" t="n">
-        <v>0.01163964626578078</v>
+        <v>0.005162250104631758</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2586.792425172231</v>
+        <v>0.6820630646121923</v>
       </c>
       <c r="B328" t="n">
-        <v>0.01094484481484885</v>
+        <v>0.01643395802585268</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2594.727371261717</v>
+        <v>0.6841552826018004</v>
       </c>
       <c r="B329" t="n">
-        <v>0.01148643040677875</v>
+        <v>0.008111792166617985</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2602.662317351202</v>
+        <v>0.6862475005914083</v>
       </c>
       <c r="B330" t="n">
-        <v>0.004136515956379388</v>
+        <v>0.01792177134183635</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2610.597263440687</v>
+        <v>0.6883397185810162</v>
       </c>
       <c r="B331" t="n">
-        <v>0.01036141357501287</v>
+        <v>0.01305814101952588</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2618.532209530173</v>
+        <v>0.6904319365706242</v>
       </c>
       <c r="B332" t="n">
-        <v>0.02363378114622098</v>
+        <v>0.004705989727151378</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2626.467155619658</v>
+        <v>0.6925241545602321</v>
       </c>
       <c r="B333" t="n">
-        <v>0.01541552122141385</v>
+        <v>0.01159227042704979</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>2634.402101709144</v>
+        <v>0.6946163725498401</v>
       </c>
       <c r="B334" t="n">
-        <v>0.006244776117483464</v>
+        <v>0.008518156005509975</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>2642.337047798629</v>
+        <v>0.696708590539448</v>
       </c>
       <c r="B335" t="n">
-        <v>0.0128972878881865</v>
+        <v>0.01770678255838557</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>2650.271993888114</v>
+        <v>0.698800808529056</v>
       </c>
       <c r="B336" t="n">
-        <v>0.03333334185796451</v>
+        <v>0.004809346563209096</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>2658.2069399776</v>
+        <v>0.7008930265186639</v>
       </c>
       <c r="B337" t="n">
-        <v>0.01666376994208461</v>
+        <v>0.0237612145622868</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2666.141886067085</v>
+        <v>0.7029852445082718</v>
       </c>
       <c r="B338" t="n">
-        <v>0.02084239078668497</v>
+        <v>0.01932325642259621</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>2674.07683215657</v>
+        <v>0.7050774624978798</v>
       </c>
       <c r="B339" t="n">
-        <v>0.01952376445980994</v>
+        <v>0.02360125775942363</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2682.011778246056</v>
+        <v>0.7071696804874877</v>
       </c>
       <c r="B340" t="n">
-        <v>0.02372071707096556</v>
+        <v>0.007334947844248851</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>2689.946724335541</v>
+        <v>0.7092618984770958</v>
       </c>
       <c r="B341" t="n">
-        <v>0.01922403582066045</v>
+        <v>0.009963971194031526</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2697.881670425026</v>
+        <v>0.7113541164667037</v>
       </c>
       <c r="B342" t="n">
-        <v>0.01965625098375406</v>
+        <v>0.02181182990095942</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>2705.816616514512</v>
+        <v>0.7134463344563117</v>
       </c>
       <c r="B343" t="n">
-        <v>0.02234543576697674</v>
+        <v>0.0187203447117238</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>2713.751562603997</v>
+        <v>0.7155385524459196</v>
       </c>
       <c r="B344" t="n">
-        <v>0.01855289646025013</v>
+        <v>0.02584420708189814</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>2721.686508693483</v>
+        <v>0.7176307704355276</v>
       </c>
       <c r="B345" t="n">
-        <v>0.01856906013276688</v>
+        <v>0.01254816955745442</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>2729.621454782968</v>
+        <v>0.7197229884251355</v>
       </c>
       <c r="B346" t="n">
-        <v>0.01489106370051913</v>
+        <v>0.00764497533817308</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2737.556400872453</v>
+        <v>0.7218152064147434</v>
       </c>
       <c r="B347" t="n">
-        <v>0.01331711603184732</v>
+        <v>0.004890117377242224</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>2745.491346961939</v>
+        <v>0.7239074244043514</v>
       </c>
       <c r="B348" t="n">
-        <v>0.006945163076231051</v>
+        <v>0.008574521362552498</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>2753.426293051424</v>
+        <v>0.7259996423939593</v>
       </c>
       <c r="B349" t="n">
-        <v>0.007515391108682012</v>
+        <v>0.009391483536172999</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2761.361239140909</v>
+        <v>0.7280918603835673</v>
       </c>
       <c r="B350" t="n">
-        <v>0.01729713616102378</v>
+        <v>0.01585237067627463</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>2769.296185230395</v>
+        <v>0.7301840783731752</v>
       </c>
       <c r="B351" t="n">
-        <v>0.02268938858193003</v>
+        <v>0.0142833629163579</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>2777.23113131988</v>
+        <v>0.7322762963627832</v>
       </c>
       <c r="B352" t="n">
-        <v>0.01451692697926991</v>
+        <v>0.01458409026891574</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2785.166077409365</v>
+        <v>0.7343685143523911</v>
       </c>
       <c r="B353" t="n">
-        <v>0.001344312844469036</v>
+        <v>0.009631661110345142</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2793.101023498851</v>
+        <v>0.7364607323419992</v>
       </c>
       <c r="B354" t="n">
-        <v>0.006926640604743229</v>
+        <v>0.01867622833579346</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2801.035969588336</v>
+        <v>0.7385529503316071</v>
       </c>
       <c r="B355" t="n">
-        <v>0.008279107034149122</v>
+        <v>0.03316264616568216</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>2808.970915677822</v>
+        <v>0.740645168321215</v>
       </c>
       <c r="B356" t="n">
-        <v>0.02546107697515811</v>
+        <v>0.03067263518150359</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>2816.905861767307</v>
+        <v>0.742737386310823</v>
       </c>
       <c r="B357" t="n">
-        <v>0.01955792544144733</v>
+        <v>0.03189841072544292</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>2824.840807856792</v>
+        <v>0.7448296043004309</v>
       </c>
       <c r="B358" t="n">
-        <v>0.01069549365898305</v>
+        <v>0.03356210173943804</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>2832.775753946278</v>
+        <v>0.7469218222900389</v>
       </c>
       <c r="B359" t="n">
-        <v>0.006468487806127903</v>
+        <v>0.03391906933964868</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>2840.710700035763</v>
+        <v>0.7490140402796468</v>
       </c>
       <c r="B360" t="n">
-        <v>0.007189048589243668</v>
+        <v>0.04890526321366305</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>2848.645646125248</v>
+        <v>0.7511062582692548</v>
       </c>
       <c r="B361" t="n">
-        <v>0.002127114737248903</v>
+        <v>0.03089181579805264</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2856.580592214734</v>
+        <v>0.7531984762588627</v>
       </c>
       <c r="B362" t="n">
-        <v>0.003943539241161956</v>
+        <v>0.008901971956410834</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>2864.515538304219</v>
+        <v>0.7552906942484707</v>
       </c>
       <c r="B363" t="n">
-        <v>0.007515505538643941</v>
+        <v>0.02133513683233279</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2872.450484393705</v>
+        <v>0.7573829122380786</v>
       </c>
       <c r="B364" t="n">
-        <v>0.0106491566462475</v>
+        <v>0.01944648073656952</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2880.38543048319</v>
+        <v>0.7594751302276865</v>
       </c>
       <c r="B365" t="n">
-        <v>0.003221801701462211</v>
+        <v>0.02568876541440497</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>2888.320376572675</v>
+        <v>0.7615673482172945</v>
       </c>
       <c r="B366" t="n">
-        <v>0.01960317803821054</v>
+        <v>0.01722207737039098</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>2896.255322662161</v>
+        <v>0.7636595662069025</v>
       </c>
       <c r="B367" t="n">
-        <v>0.01346729785720618</v>
+        <v>0.01477778634228658</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>2904.190268751646</v>
+        <v>0.7657517841965105</v>
       </c>
       <c r="B368" t="n">
-        <v>0.01252302679001041</v>
+        <v>0.01475296430699645</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>2912.125214841131</v>
+        <v>0.7678440021861184</v>
       </c>
       <c r="B369" t="n">
-        <v>0.01943233863475664</v>
+        <v>0.01633878811120859</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>2920.060160930617</v>
+        <v>0.7699362201757264</v>
       </c>
       <c r="B370" t="n">
-        <v>0.01039449743605526</v>
+        <v>0.007808222268281177</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>2927.995107020102</v>
+        <v>0.7720284381653343</v>
       </c>
       <c r="B371" t="n">
-        <v>0.01659882690866981</v>
+        <v>0.0009181146958709337</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>2935.930053109587</v>
+        <v>0.7741206561549423</v>
       </c>
       <c r="B372" t="n">
-        <v>0.01088974572279311</v>
+        <v>0.009904111072556737</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>2943.864999199073</v>
+        <v>0.7762128741445502</v>
       </c>
       <c r="B373" t="n">
-        <v>0.01728482137725171</v>
+        <v>0.02046543800653646</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>2951.799945288558</v>
+        <v>0.7783050921341581</v>
       </c>
       <c r="B374" t="n">
-        <v>0.006800272676424662</v>
+        <v>0.02116774376548279</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>2959.734891378044</v>
+        <v>0.7803973101237661</v>
       </c>
       <c r="B375" t="n">
-        <v>0.009907432670694919</v>
+        <v>0.01729458722527668</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>2967.669837467529</v>
+        <v>0.782489528113374</v>
       </c>
       <c r="B376" t="n">
-        <v>0.01136298148722773</v>
+        <v>0.01917816097702223</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>2975.604783557014</v>
+        <v>0.784581746102982</v>
       </c>
       <c r="B377" t="n">
-        <v>0.01129252988579736</v>
+        <v>0.02176066537476943</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>2983.5397296465</v>
+        <v>0.7866739640925899</v>
       </c>
       <c r="B378" t="n">
-        <v>0.007020795942603135</v>
+        <v>0.02141401556262385</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>2991.474675735985</v>
+        <v>0.788766182082198</v>
       </c>
       <c r="B379" t="n">
-        <v>0.02098599905505065</v>
+        <v>0.01237176169659442</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>2999.40962182547</v>
+        <v>0.7908584000718059</v>
       </c>
       <c r="B380" t="n">
-        <v>0.01190491686895814</v>
+        <v>0.008569546717193972</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>3007.344567914956</v>
+        <v>0.7929506180614138</v>
       </c>
       <c r="B381" t="n">
-        <v>0.0136851277541918</v>
+        <v>0.02098245292630884</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>3015.279514004441</v>
+        <v>0.7950428360510218</v>
       </c>
       <c r="B382" t="n">
-        <v>0.003941881001322784</v>
+        <v>0.01644767524158807</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>3023.214460093926</v>
+        <v>0.7971350540406297</v>
       </c>
       <c r="B383" t="n">
-        <v>0.002790821254540334</v>
+        <v>0.00869080802438453</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>3031.149406183412</v>
+        <v>0.7992272720302377</v>
       </c>
       <c r="B384" t="n">
-        <v>0.005104321940042292</v>
+        <v>0.01469502775585189</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>3039.084352272897</v>
+        <v>0.8013194900198456</v>
       </c>
       <c r="B385" t="n">
-        <v>0.006932926107445387</v>
+        <v>0.00932550499619241</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>3047.019298362383</v>
+        <v>0.8034117080094536</v>
       </c>
       <c r="B386" t="n">
-        <v>0.005123539279790742</v>
+        <v>0.01052297316268261</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>3054.954244451868</v>
+        <v>0.8055039259990615</v>
       </c>
       <c r="B387" t="n">
-        <v>0.008987724828816279</v>
+        <v>0.0138035315679782</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>3062.889190541353</v>
+        <v>0.8075961439886695</v>
       </c>
       <c r="B388" t="n">
-        <v>0.01363394506413405</v>
+        <v>0.0167051297991352</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>3070.824136630839</v>
+        <v>0.8096883619782774</v>
       </c>
       <c r="B389" t="n">
-        <v>0.002582319958178226</v>
+        <v>0.02571630352098868</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>3078.759082720324</v>
+        <v>0.8117805799678853</v>
       </c>
       <c r="B390" t="n">
-        <v>0.01163222368451003</v>
+        <v>0.02490807312010054</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>3086.694028809809</v>
+        <v>0.8138727979574933</v>
       </c>
       <c r="B391" t="n">
-        <v>0.0151662178526602</v>
+        <v>0.01926249218224099</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>3094.628974899295</v>
+        <v>0.8159650159471012</v>
       </c>
       <c r="B392" t="n">
-        <v>0.01100638828466269</v>
+        <v>0.01339951566251355</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>3102.56392098878</v>
+        <v>0.8180572339367093</v>
       </c>
       <c r="B393" t="n">
-        <v>0.01319742320322675</v>
+        <v>0.002051561269441737</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>3110.498867078266</v>
+        <v>0.8201494519263172</v>
       </c>
       <c r="B394" t="n">
-        <v>0.01876328233350087</v>
+        <v>0.009500745706886381</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>3118.433813167751</v>
+        <v>0.8222416699159252</v>
       </c>
       <c r="B395" t="n">
-        <v>0.01606573109706023</v>
+        <v>0.01770182002345391</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>3126.368759257236</v>
+        <v>0.8243338879055331</v>
       </c>
       <c r="B396" t="n">
-        <v>0.01623943320293644</v>
+        <v>0.004137496503226883</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>3134.303705346722</v>
+        <v>0.8264261058951411</v>
       </c>
       <c r="B397" t="n">
-        <v>0.02136659106854584</v>
+        <v>0.006084550620403551</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>3142.238651436207</v>
+        <v>0.828518323884749</v>
       </c>
       <c r="B398" t="n">
-        <v>0.02052624468012262</v>
+        <v>0.008086224225734124</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>3150.173597525692</v>
+        <v>0.8306105418743569</v>
       </c>
       <c r="B399" t="n">
-        <v>0.0133336710434223</v>
+        <v>0.01635701821675926</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>3158.108543615178</v>
+        <v>0.8327027598639649</v>
       </c>
       <c r="B400" t="n">
-        <v>0.01715203257131783</v>
+        <v>0.02873290710231385</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>3166.043489704663</v>
+        <v>0.8347949778535728</v>
       </c>
       <c r="B401" t="n">
-        <v>0.01379418379425254</v>
+        <v>0.01390923957843843</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>3173.978435794148</v>
+        <v>0.8368871958431808</v>
       </c>
       <c r="B402" t="n">
-        <v>0.01517970292859803</v>
+        <v>0.01598656528680399</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>3181.913381883634</v>
+        <v>0.8389794138327887</v>
       </c>
       <c r="B403" t="n">
-        <v>0.01844844729906719</v>
+        <v>0.00510081848942308</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>3189.848327973119</v>
+        <v>0.8410716318223967</v>
       </c>
       <c r="B404" t="n">
-        <v>0.02161185059694678</v>
+        <v>0.005562342413041589</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>3197.783274062605</v>
+        <v>0.8431638498120047</v>
       </c>
       <c r="B405" t="n">
-        <v>0.01647305394813271</v>
+        <v>0.02132246229945172</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>3205.71822015209</v>
+        <v>0.8452560678016127</v>
       </c>
       <c r="B406" t="n">
-        <v>0.002226589576150047</v>
+        <v>0.01335248284550728</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>3213.653166241575</v>
+        <v>0.8473482857912206</v>
       </c>
       <c r="B407" t="n">
-        <v>0.001471453795003022</v>
+        <v>0.01117858868162802</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>3221.588112331061</v>
+        <v>0.8494405037808285</v>
       </c>
       <c r="B408" t="n">
-        <v>0.01041446993479634</v>
+        <v>0.01893863813367906</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>3229.523058420546</v>
+        <v>0.8515327217704365</v>
       </c>
       <c r="B409" t="n">
-        <v>0.002873330095553572</v>
+        <v>0.01202498821726471</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>3237.458004510032</v>
+        <v>0.8536249397600444</v>
       </c>
       <c r="B410" t="n">
-        <v>0.01185780987758498</v>
+        <v>0.009972534553322488</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>3245.392950599517</v>
+        <v>0.8557171577496524</v>
       </c>
       <c r="B411" t="n">
-        <v>0.01127172615379563</v>
+        <v>0.009118235496962605</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>3253.327896689003</v>
+        <v>0.8578093757392603</v>
       </c>
       <c r="B412" t="n">
-        <v>0.01132349915740382</v>
+        <v>0.004847597088410184</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>3261.262842778488</v>
+        <v>0.8599015937288683</v>
       </c>
       <c r="B413" t="n">
-        <v>0.01530977453234267</v>
+        <v>0.01620849694084729</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>3269.197788867973</v>
+        <v>0.8619938117184762</v>
       </c>
       <c r="B414" t="n">
-        <v>0.01018577745224017</v>
+        <v>0.02260992835814695</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>3277.132734957459</v>
+        <v>0.8640860297080842</v>
       </c>
       <c r="B415" t="n">
-        <v>0.01110274032575057</v>
+        <v>0.02501786611658331</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>3285.067681046944</v>
+        <v>0.8661782476976921</v>
       </c>
       <c r="B416" t="n">
-        <v>0.01964154397239276</v>
+        <v>0.01281676761485977</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>3293.002627136429</v>
+        <v>0.8682704656873</v>
       </c>
       <c r="B417" t="n">
-        <v>0.01419745601119775</v>
+        <v>0.01132274217967876</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>3300.937573225915</v>
+        <v>0.8703626836769081</v>
       </c>
       <c r="B418" t="n">
-        <v>0.006585899242790043</v>
+        <v>0.01041334883074351</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>3308.8725193154</v>
+        <v>0.872454901666516</v>
       </c>
       <c r="B419" t="n">
-        <v>0.01677216496782476</v>
+        <v>0.01113339989029084</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>3316.807465404886</v>
+        <v>0.874547119656124</v>
       </c>
       <c r="B420" t="n">
-        <v>0.01204648067500056</v>
+        <v>0.01713921045701239</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>3324.742411494371</v>
+        <v>0.8766393376457319</v>
       </c>
       <c r="B421" t="n">
-        <v>0.01006539560129156</v>
+        <v>0.01035987921431564</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>3332.677357583856</v>
+        <v>0.8787315556353399</v>
       </c>
       <c r="B422" t="n">
-        <v>0.003291429583262308</v>
+        <v>0.0101474336233887</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>3340.612303673342</v>
+        <v>0.8808237736249478</v>
       </c>
       <c r="B423" t="n">
-        <v>0.00898019920662977</v>
+        <v>0.0286043876532776</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>0.8829159916145558</v>
+      </c>
+      <c r="B424" t="n">
+        <v>0.02337509481310061</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>0.8850082096041637</v>
+      </c>
+      <c r="B425" t="n">
+        <v>0.005990930274482325</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>0.8871004275937716</v>
+      </c>
+      <c r="B426" t="n">
+        <v>0.01573388892059425</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>0.8891926455833796</v>
+      </c>
+      <c r="B427" t="n">
+        <v>0.01075941357140932</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>0.8912848635729875</v>
+      </c>
+      <c r="B428" t="n">
+        <v>0.006372508213102184</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>0.8933770815625955</v>
+      </c>
+      <c r="B429" t="n">
+        <v>0.01077143604087743</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>0.8954692995522034</v>
+      </c>
+      <c r="B430" t="n">
+        <v>0.007771610780621513</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>0.8975615175418115</v>
+      </c>
+      <c r="B431" t="n">
+        <v>0.01986618727870071</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>0.8996537355314194</v>
+      </c>
+      <c r="B432" t="n">
+        <v>0.01222380640886174</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>0.9017459535210273</v>
+      </c>
+      <c r="B433" t="n">
+        <v>0.02265947797011328</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>0.9038381715106353</v>
+      </c>
+      <c r="B434" t="n">
+        <v>0.005418433244427608</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>0.9059303895002432</v>
+      </c>
+      <c r="B435" t="n">
+        <v>0.009654901002278525</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>0.9080226074898512</v>
+      </c>
+      <c r="B436" t="n">
+        <v>0.01534654335470984</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>0.9101148254794591</v>
+      </c>
+      <c r="B437" t="n">
+        <v>0.01433761041043509</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>0.9122070434690671</v>
+      </c>
+      <c r="B438" t="n">
+        <v>0.02038417323017612</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>0.914299261458675</v>
+      </c>
+      <c r="B439" t="n">
+        <v>0.01085549675653232</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>0.916391479448283</v>
+      </c>
+      <c r="B440" t="n">
+        <v>0.006406080583101716</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>0.9184836974378909</v>
+      </c>
+      <c r="B441" t="n">
+        <v>0.01671433116724494</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>0.9205759154274988</v>
+      </c>
+      <c r="B442" t="n">
+        <v>0.01524715926174455</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>0.9226681334171069</v>
+      </c>
+      <c r="B443" t="n">
+        <v>0.006292087075092588</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>0.9247603514067148</v>
+      </c>
+      <c r="B444" t="n">
+        <v>0.01592480289122891</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>0.9268525693963228</v>
+      </c>
+      <c r="B445" t="n">
+        <v>0.01355735990017488</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>0.9289447873859307</v>
+      </c>
+      <c r="B446" t="n">
+        <v>0.0077067269647941</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>0.9310370053755387</v>
+      </c>
+      <c r="B447" t="n">
+        <v>0.008497341324185741</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>0.9331292233651466</v>
+      </c>
+      <c r="B448" t="n">
+        <v>0.008324010591610352</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>0.9352214413547546</v>
+      </c>
+      <c r="B449" t="n">
+        <v>0.007169202872419614</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>0.9373136593443625</v>
+      </c>
+      <c r="B450" t="n">
+        <v>0.0192042049716106</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>0.9394058773339704</v>
+      </c>
+      <c r="B451" t="n">
+        <v>0.01425608335886221</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>0.9414980953235784</v>
+      </c>
+      <c r="B452" t="n">
+        <v>0.02096256903237368</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>0.9435903133131863</v>
+      </c>
+      <c r="B453" t="n">
+        <v>0.02049052496469832</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>0.9456825313027943</v>
+      </c>
+      <c r="B454" t="n">
+        <v>0.01424577196493656</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>0.9477747492924022</v>
+      </c>
+      <c r="B455" t="n">
+        <v>0.01535009353859135</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>0.9498669672820103</v>
+      </c>
+      <c r="B456" t="n">
+        <v>0.02142377820512969</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>0.9519591852716182</v>
+      </c>
+      <c r="B457" t="n">
+        <v>0.01669544620008258</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>0.9540514032612262</v>
+      </c>
+      <c r="B458" t="n">
+        <v>0.009826843607359201</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>0.9561436212508341</v>
+      </c>
+      <c r="B459" t="n">
+        <v>0.01667417401468775</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>0.958235839240442</v>
+      </c>
+      <c r="B460" t="n">
+        <v>0.02604350802936108</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>0.96032805723005</v>
+      </c>
+      <c r="B461" t="n">
+        <v>0.02017930225138975</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>0.9624202752196579</v>
+      </c>
+      <c r="B462" t="n">
+        <v>0.004875824815265384</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>0.9645124932092659</v>
+      </c>
+      <c r="B463" t="n">
+        <v>0.01894020483001303</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>0.9666047111988738</v>
+      </c>
+      <c r="B464" t="n">
+        <v>0.02634016578762085</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>0.9686969291884818</v>
+      </c>
+      <c r="B465" t="n">
+        <v>0.01548925480897051</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>0.9707891471780897</v>
+      </c>
+      <c r="B466" t="n">
+        <v>0.003639253554073857</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>0.9728813651676977</v>
+      </c>
+      <c r="B467" t="n">
+        <v>0.008750323025219088</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>0.9749735831573056</v>
+      </c>
+      <c r="B468" t="n">
+        <v>0.01588241771556873</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>0.9770658011469135</v>
+      </c>
+      <c r="B469" t="n">
+        <v>0.007390844278856682</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>0.9791580191365216</v>
+      </c>
+      <c r="B470" t="n">
+        <v>0.01020504137725671</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>0.9812502371261295</v>
+      </c>
+      <c r="B471" t="n">
+        <v>0.01144695828482972</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>0.9833424551157375</v>
+      </c>
+      <c r="B472" t="n">
+        <v>0.01075834507528619</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>0.9854346731053454</v>
+      </c>
+      <c r="B473" t="n">
+        <v>0.01861167083851234</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>0.9875268910949534</v>
+      </c>
+      <c r="B474" t="n">
+        <v>0.02485589809415801</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>0.9896191090845613</v>
+      </c>
+      <c r="B475" t="n">
+        <v>0.01134230765297493</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>0.9917113270741692</v>
+      </c>
+      <c r="B476" t="n">
+        <v>0.01149672101737734</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>0.9938035450637772</v>
+      </c>
+      <c r="B477" t="n">
+        <v>0.0138201109378908</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>0.9958957630533851</v>
+      </c>
+      <c r="B478" t="n">
+        <v>0.005947849900618201</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>0.9979879810429931</v>
+      </c>
+      <c r="B479" t="n">
+        <v>0.008088025002027393</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>1.000080199032601</v>
+      </c>
+      <c r="B480" t="n">
+        <v>0.01888197939844874</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>1.002172417022209</v>
+      </c>
+      <c r="B481" t="n">
+        <v>0.02590773222803122</v>
       </c>
     </row>
   </sheetData>
@@ -3919,12 +4383,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Lum</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.6</t>
         </is>
       </c>
     </row>
